--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32547,12 +32547,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32557,7 +32557,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32557,7 +32557,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32631,7 +32631,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32557,7 +32557,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32584,17 +32584,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -32631,7 +32631,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32557,7 +32557,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32589,12 +32589,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32552,12 +32552,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32621,12 +32621,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32658,12 +32658,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32695,12 +32695,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32732,12 +32732,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -151,17 +151,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -171,12 +171,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.0</t>
+          <t xml:space="preserve">44.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -186,12 +186,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-26</t>
+          <t xml:space="preserve">2026-04-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.12.25</t>
+          <t xml:space="preserve">29.04.26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -226,24 +226,24 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-2</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -253,12 +253,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27</t>
+          <t xml:space="preserve">hek ki 8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.0</t>
+          <t xml:space="preserve">44.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -268,12 +268,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-26</t>
+          <t xml:space="preserve">2026-04-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.12.25</t>
+          <t xml:space="preserve">29.04.26</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -303,24 +308,24 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-3</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -330,12 +335,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27</t>
+          <t xml:space="preserve">hek ki 8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.0</t>
+          <t xml:space="preserve">45.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -345,12 +350,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-26</t>
+          <t xml:space="preserve">2026-04-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.12.25</t>
+          <t xml:space="preserve">29.04.26</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -380,24 +390,24 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-4</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -407,12 +417,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os</t>
+          <t xml:space="preserve">hek ki 8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.0</t>
+          <t xml:space="preserve">45.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -422,12 +432,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-20</t>
+          <t xml:space="preserve">2026-04-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.04.26</t>
+          <t xml:space="preserve">29.04.26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -457,24 +472,24 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-5</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -484,12 +499,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hn30</t>
+          <t xml:space="preserve">hek ki 6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.0</t>
+          <t xml:space="preserve">45.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -497,19 +512,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.05.25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">29.04.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HN30</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -539,24 +554,24 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-6</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -566,12 +581,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fadu</t>
+          <t xml:space="preserve">hek ki 6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.0</t>
+          <t xml:space="preserve">45.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -579,19 +594,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.05.25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">29.04.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -621,24 +636,24 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-7</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -648,12 +663,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hn30</t>
+          <t xml:space="preserve">hek ki 6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.0</t>
+          <t xml:space="preserve">46.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -661,19 +676,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-18</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.05.25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">18.04.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HN30</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -703,24 +718,24 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-8</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -730,12 +745,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">hn30</t>
+          <t xml:space="preserve">hek ki 6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.0</t>
+          <t xml:space="preserve">45.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -745,17 +760,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-28</t>
+          <t xml:space="preserve">2026-04-29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.01.26</t>
+          <t xml:space="preserve">29.04.26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HN30</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -785,24 +800,24 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-9</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -812,37 +827,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21.0</t>
+          <t xml:space="preserve">mda mpg ox</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-27</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.06.25</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">26.05.26</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -867,24 +872,24 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-10</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -894,12 +899,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fadu</t>
+          <t xml:space="preserve">hek ki 5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -907,19 +912,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.05.25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">29.04.26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -949,24 +954,24 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-11</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -976,12 +981,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">fadu</t>
+          <t xml:space="preserve">hek ki 5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -989,19 +994,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-30</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.01.26</t>
+          <t xml:space="preserve">01.05.26</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1031,24 +1036,24 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-12</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1058,12 +1063,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">u373</t>
+          <t xml:space="preserve">hek ki 5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1071,14 +1076,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-30</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.01.26</t>
+          <t xml:space="preserve">01.05.26</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1108,24 +1118,24 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-13</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1135,12 +1145,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">fadu</t>
+          <t xml:space="preserve">hek ki 5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.0</t>
+          <t xml:space="preserve">34.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1150,7 +1160,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.05.25</t>
+          <t xml:space="preserve">01.05.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1160,7 +1170,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1190,24 +1200,24 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-14</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1217,12 +1227,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">hn30</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1230,24 +1240,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-15</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">02.05.25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HN30</t>
+          <t xml:space="preserve">15.05.26</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1272,24 +1277,24 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-15</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1299,12 +1304,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1314,17 +1319,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-20</t>
+          <t xml:space="preserve">2026-05-15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.02.26</t>
+          <t xml:space="preserve">15.05.26</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1349,24 +1354,24 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-16</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1376,12 +1381,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.0</t>
+          <t xml:space="preserve">23.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1389,19 +1394,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-15</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.11.25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">15.05.26</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1431,24 +1431,24 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-17</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">12.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-25</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.11.25</t>
+          <t xml:space="preserve">26.05.26</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-18</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">12.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">26.05.26</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1585,24 +1585,24 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-19</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os mpg ox</t>
+          <t xml:space="preserve">hek nek2 ox</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1627,12 +1627,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">25.05.26</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1662,24 +1667,24 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-20</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1689,7 +1694,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox</t>
+          <t xml:space="preserve">hek nek2 ox</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1704,12 +1709,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">25.05.26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1744,24 +1749,24 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-21</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1771,7 +1776,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox</t>
+          <t xml:space="preserve">hek nek2 ox</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1786,12 +1791,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">25.05.26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1826,24 +1831,24 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-22</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1853,12 +1858,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os mpg ox</t>
+          <t xml:space="preserve">hek nek2 ox</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1868,12 +1873,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">25.05.26</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1903,24 +1913,24 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-23</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1930,7 +1940,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1945,17 +1955,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">25.05.26</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1985,24 +1990,24 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-24</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2012,12 +2017,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda mpg ox</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2027,12 +2032,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">25.05.26</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2062,24 +2067,24 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-25</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2089,12 +2094,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os mpg ox</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2104,12 +2109,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">25.05.26</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2139,24 +2144,24 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-26</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2171,7 +2176,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">12.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2181,12 +2186,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">26.05.26</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2216,24 +2221,24 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-27</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2243,12 +2248,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os mpg ox</t>
+          <t xml:space="preserve">u2os dox mpg 3</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2258,12 +2263,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-05-29</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">29.05.26</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2293,24 +2298,24 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-28</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2320,12 +2325,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2</t>
+          <t xml:space="preserve">hek nek2 ox</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2335,12 +2340,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-27</t>
+          <t xml:space="preserve">2026-05-28</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.04.26</t>
+          <t xml:space="preserve">28.05.26</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2370,24 +2380,24 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-29</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2402,7 +2412,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2410,14 +2420,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-28</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.08.25</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">28.05.26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2452,24 +2462,24 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-30</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2484,7 +2494,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2492,14 +2502,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-28</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.25</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">28.05.26</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2534,24 +2544,24 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-31</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2561,27 +2571,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ko b9</t>
+          <t xml:space="preserve">mda nek2 ox</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-23</t>
+          <t xml:space="preserve">2026-05-28</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.01.25</t>
+          <t xml:space="preserve">28.05.26</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2606,24 +2621,24 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-32</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2633,12 +2648,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 k37r</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2648,17 +2663,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-30</t>
+          <t xml:space="preserve">2026-05-28</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.05.25</t>
+          <t xml:space="preserve">28.05.26</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2683,24 +2698,24 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-33</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2710,12 +2725,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ko b5</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2725,17 +2740,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-22</t>
+          <t xml:space="preserve">2026-05-28</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.01.25</t>
+          <t xml:space="preserve">28.05.26</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2760,24 +2775,24 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-34</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2787,12 +2802,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 k37r</t>
+          <t xml:space="preserve">u2os dox mpg 3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2802,17 +2817,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-22</t>
+          <t xml:space="preserve">2026-05-29</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.01.25</t>
+          <t xml:space="preserve">29.05.26</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2837,24 +2852,24 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-35</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2864,12 +2879,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 k37r</t>
+          <t xml:space="preserve">u2os dox mpg 3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2879,17 +2894,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-30</t>
+          <t xml:space="preserve">2026-05-29</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.05.25</t>
+          <t xml:space="preserve">29.05.26</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2914,24 +2929,24 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-36</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2941,12 +2956,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ko b9</t>
+          <t xml:space="preserve">u2os dox mpg 3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2956,17 +2971,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-22</t>
+          <t xml:space="preserve">2026-05-29</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.01.25</t>
+          <t xml:space="preserve">29.05.26</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2991,24 +3006,24 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-37</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3018,12 +3033,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">u2os dox mpg 1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3031,14 +3046,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-29</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.08.25</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">29.05.26</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3068,24 +3083,24 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-38</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3095,12 +3110,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox</t>
+          <t xml:space="preserve">u2os dox mpg 1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3108,19 +3123,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-29</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.25</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">29.05.26</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3150,24 +3160,24 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-39</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3177,12 +3187,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox</t>
+          <t xml:space="preserve">u2os dox mpg 1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3190,19 +3200,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-29</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.08.25</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">29.05.26</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3232,24 +3237,24 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-40</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3259,12 +3264,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox</t>
+          <t xml:space="preserve">hek mpg ox</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">14.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3274,12 +3279,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-05-29</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">29.05.26</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3309,24 +3319,24 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-41</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3336,12 +3346,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox</t>
+          <t xml:space="preserve">hek mpg ox</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">14.0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3351,12 +3361,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-05-29</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">29.05.26</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3386,24 +3401,24 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-42</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3413,12 +3428,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox</t>
+          <t xml:space="preserve">hek apex1 ox</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">21.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3428,12 +3443,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">27.07.26</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3463,24 +3483,24 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-43</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3490,12 +3510,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox</t>
+          <t xml:space="preserve">u2os dox nek2 ox</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">12.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3505,12 +3525,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-05-25</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">25.05.26</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3540,24 +3560,24 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-44</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3567,12 +3587,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox</t>
+          <t xml:space="preserve">hek nek2 ox</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">29.0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3582,12 +3602,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-05-29</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">29.05.26</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3617,24 +3642,24 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-45</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3644,12 +3669,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">19.0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3659,17 +3684,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-06-25</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">25.06.26</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3694,24 +3724,24 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-46</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3721,12 +3751,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox</t>
+          <t xml:space="preserve">hek apex1 ox</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3736,12 +3766,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">15.06.26</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3771,24 +3806,24 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-47</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3798,12 +3833,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox</t>
+          <t xml:space="preserve">hek shgfp</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3813,17 +3848,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">15.06.26</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3838,7 +3878,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -3848,24 +3888,24 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-48</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3875,12 +3915,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2</t>
+          <t xml:space="preserve">mda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">29.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3890,17 +3930,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-06-25</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">25.06.26</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3925,24 +3965,24 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-49</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3952,12 +3992,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox sh nek2</t>
+          <t xml:space="preserve">u2os dox mpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3967,12 +4007,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-07-24</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">24.07.26</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3992,7 +4032,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4002,24 +4042,24 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-50</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4029,12 +4069,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2</t>
+          <t xml:space="preserve">u2os dox mpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4044,12 +4084,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-17</t>
+          <t xml:space="preserve">2026-07-24</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.02.26</t>
+          <t xml:space="preserve">24.07.26</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4079,24 +4119,24 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-51</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4106,12 +4146,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2</t>
+          <t xml:space="preserve">mda dox mpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.0</t>
+          <t xml:space="preserve">21.0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4121,12 +4161,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-27</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.04.26</t>
+          <t xml:space="preserve">27.07.26</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4156,24 +4196,24 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-52</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4183,12 +4223,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">hek dox mpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">14.0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4198,12 +4238,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-18</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.03.26</t>
+          <t xml:space="preserve">27.07.26</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4233,24 +4278,24 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-53</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4260,12 +4305,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox</t>
+          <t xml:space="preserve">mda shgfp</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">25.0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4275,17 +4320,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">27.07.26</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4300,7 +4345,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4310,24 +4355,24 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-54</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4337,12 +4382,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek shgfp</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.0</t>
+          <t xml:space="preserve">15.0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4352,12 +4397,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
+          <t xml:space="preserve">27.07.26</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4382,7 +4427,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -4392,24 +4437,24 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-55</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4419,7 +4464,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">u2os dox sh nek2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4434,22 +4479,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.03.26</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">27.07.26</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4464,7 +4504,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -4474,24 +4514,24 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-56</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4501,27 +4541,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox</t>
+          <t xml:space="preserve">u2os dox nek2</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-22</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.07.25</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">27.07.26</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4551,24 +4591,24 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-57</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4578,12 +4618,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 200</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4593,12 +4633,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-27</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.06.25</t>
+          <t xml:space="preserve">21.04.25</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4608,7 +4648,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4633,24 +4673,24 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-58</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4660,12 +4700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 50</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4675,12 +4715,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.05.25</t>
+          <t xml:space="preserve">21.04.25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4690,7 +4730,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4715,24 +4755,24 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-59</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4742,12 +4782,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.0</t>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4755,14 +4795,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.05.25</t>
+          <t xml:space="preserve">03.01.25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4772,7 +4812,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4797,24 +4837,24 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-60</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4824,12 +4864,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh elk1 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4837,14 +4877,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-21</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.09.25</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">21.04.25</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4864,7 +4909,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -4874,24 +4919,24 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-61</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4901,12 +4946,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh elf1 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.0</t>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4914,14 +4959,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-15</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">09.07.25</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">15.05.25</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4941,7 +4991,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -4951,24 +5001,24 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-62</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4978,12 +5028,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 shgfp 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">10.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4991,14 +5041,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-02-14</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.09.25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">14.02.25</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5018,7 +5073,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5028,24 +5083,24 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-63</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5055,12 +5110,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh creb1 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5068,14 +5123,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-21</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.09.25</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">21.04.25</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5095,7 +5155,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5105,24 +5165,24 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-64</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5132,12 +5192,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh klf4 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5145,14 +5205,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-21</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.09.25</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">21.04.25</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5172,7 +5237,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5182,24 +5247,24 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-65</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5209,12 +5274,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh elf1 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">17.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5224,7 +5289,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.09.25</t>
+          <t xml:space="preserve">06.01.25</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5232,6 +5297,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5249,7 +5319,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -5259,24 +5329,24 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-66</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5286,12 +5356,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 200</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5301,12 +5371,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-26</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.05.25</t>
+          <t xml:space="preserve">21.04.25</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5316,7 +5386,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5341,24 +5411,24 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-67</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5368,12 +5438,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh klf4 200</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5381,14 +5451,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-21</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">09.07.25</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">21.04.25</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5408,7 +5483,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -5418,24 +5493,24 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-68</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5445,12 +5520,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh elk1 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5458,14 +5533,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-21</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">09.07.25</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">21.04.25</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5485,7 +5565,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -5495,24 +5575,24 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-69</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5522,12 +5602,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh creb1 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5535,14 +5615,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-21</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">09.07.25</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">21.04.25</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5562,7 +5647,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -5572,24 +5657,24 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-70</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5599,12 +5684,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 shgfp 100</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.0</t>
+          <t xml:space="preserve">18.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5612,14 +5697,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-21</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">09.07.25</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">21.04.25</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5639,7 +5729,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -5649,7 +5739,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-71</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -5671,17 +5761,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 5</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.0</t>
+          <t xml:space="preserve">10.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5691,12 +5781,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-21</t>
+          <t xml:space="preserve">2025-12-26</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.11.25</t>
+          <t xml:space="preserve">26.12.25</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5731,7 +5821,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-72</t>
+          <t xml:space="preserve">v-2</t>
         </is>
       </c>
     </row>
@@ -5753,17 +5843,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8</t>
+          <t xml:space="preserve">cal27</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">43.0</t>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5773,17 +5863,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-21</t>
+          <t xml:space="preserve">2025-12-26</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.11.24</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">26.12.25</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5813,7 +5898,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-73</t>
+          <t xml:space="preserve">v-3</t>
         </is>
       </c>
     </row>
@@ -5835,17 +5920,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek gnt</t>
+          <t xml:space="preserve">cal27</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5855,17 +5940,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-18</t>
+          <t xml:space="preserve">2025-12-26</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.04.25</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">26.12.25</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5895,7 +5975,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-74</t>
+          <t xml:space="preserve">v-4</t>
         </is>
       </c>
     </row>
@@ -5917,17 +5997,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8 mtf1 ox</t>
+          <t xml:space="preserve">u2os</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.0</t>
+          <t xml:space="preserve">17.0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5935,24 +6015,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-20</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">05.05.25</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">20.04.26</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5977,7 +6052,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-75</t>
+          <t xml:space="preserve">v-5</t>
         </is>
       </c>
     </row>
@@ -5999,17 +6074,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8</t>
+          <t xml:space="preserve">hn30</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.0</t>
+          <t xml:space="preserve">20.0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6019,7 +6094,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">06.01.25</t>
+          <t xml:space="preserve">02.05.25</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6029,7 +6104,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HN30</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6059,7 +6134,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-76</t>
+          <t xml:space="preserve">v-6</t>
         </is>
       </c>
     </row>
@@ -6081,17 +6156,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8</t>
+          <t xml:space="preserve">fadu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">54.0</t>
+          <t xml:space="preserve">19.0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6101,7 +6176,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">03.01.25</t>
+          <t xml:space="preserve">02.05.25</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6111,7 +6186,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6141,7 +6216,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-77</t>
+          <t xml:space="preserve">v-7</t>
         </is>
       </c>
     </row>
@@ -6163,17 +6238,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 6</t>
+          <t xml:space="preserve">hn30</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">43.0</t>
+          <t xml:space="preserve">20.0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6181,19 +6256,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2024-11-21</t>
-        </is>
-      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.11.24</t>
+          <t xml:space="preserve">02.05.25</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HN30</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6223,7 +6298,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-78</t>
+          <t xml:space="preserve">v-8</t>
         </is>
       </c>
     </row>
@@ -6245,17 +6320,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8</t>
+          <t xml:space="preserve">hn30</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">48.0</t>
+          <t xml:space="preserve">11.0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6265,17 +6340,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-14</t>
+          <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.02.25</t>
+          <t xml:space="preserve">28.01.26</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HN30</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6305,7 +6380,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-79</t>
+          <t xml:space="preserve">v-9</t>
         </is>
       </c>
     </row>
@@ -6327,17 +6402,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 5</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">39.0</t>
+          <t xml:space="preserve">21.0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6347,12 +6422,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-14</t>
+          <t xml:space="preserve">2025-06-27</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.02.25</t>
+          <t xml:space="preserve">27.06.25</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6387,7 +6462,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-80</t>
+          <t xml:space="preserve">v-10</t>
         </is>
       </c>
     </row>
@@ -6409,17 +6484,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8</t>
+          <t xml:space="preserve">fadu</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">43.0</t>
+          <t xml:space="preserve">19.0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6427,19 +6502,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2024-11-21</t>
-        </is>
-      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.11.24</t>
+          <t xml:space="preserve">02.05.25</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6469,7 +6544,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-81</t>
+          <t xml:space="preserve">v-11</t>
         </is>
       </c>
     </row>
@@ -6491,17 +6566,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">I9</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 6</t>
+          <t xml:space="preserve">fadu</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">49.0</t>
+          <t xml:space="preserve">11.0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6511,17 +6586,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-21</t>
+          <t xml:space="preserve">2026-01-30</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.11.24</t>
+          <t xml:space="preserve">30.01.26</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6551,7 +6626,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-82</t>
+          <t xml:space="preserve">v-12</t>
         </is>
       </c>
     </row>
@@ -6568,22 +6643,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8</t>
+          <t xml:space="preserve">u373</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.0</t>
+          <t xml:space="preserve">21.0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6593,17 +6668,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-29</t>
+          <t xml:space="preserve">2026-01-30</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.04.26</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">30.01.26</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6633,7 +6703,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-13</t>
         </is>
       </c>
     </row>
@@ -6650,22 +6720,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8</t>
+          <t xml:space="preserve">fadu</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.0</t>
+          <t xml:space="preserve">19.0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6673,19 +6743,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-29</t>
-        </is>
-      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.04.26</t>
+          <t xml:space="preserve">02.05.25</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6715,7 +6785,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-14</t>
         </is>
       </c>
     </row>
@@ -6732,22 +6802,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8</t>
+          <t xml:space="preserve">hn30</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">45.0</t>
+          <t xml:space="preserve">20.0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6755,19 +6825,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-29</t>
-        </is>
-      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.04.26</t>
+          <t xml:space="preserve">02.05.25</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HN30</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6797,7 +6867,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-15</t>
         </is>
       </c>
     </row>
@@ -6814,22 +6884,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8</t>
+          <t xml:space="preserve">u2os</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">45.0</t>
+          <t xml:space="preserve">17.0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6839,17 +6909,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-29</t>
+          <t xml:space="preserve">2026-02-20</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.04.26</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">20.02.26</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6879,7 +6944,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-16</t>
         </is>
       </c>
     </row>
@@ -6896,22 +6961,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 6</t>
+          <t xml:space="preserve">hek mpg ox</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">45.0</t>
+          <t xml:space="preserve">5.0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6919,14 +6984,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-29</t>
-        </is>
-      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.04.26</t>
+          <t xml:space="preserve">7.11.25</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6936,7 +7001,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6961,7 +7026,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-17</t>
         </is>
       </c>
     </row>
@@ -6978,22 +7043,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 6</t>
+          <t xml:space="preserve">mda mpg ox</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">45.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7003,22 +7068,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-29</t>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.04.26</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">25.11.25</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7043,7 +7103,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-18</t>
         </is>
       </c>
     </row>
@@ -7060,22 +7120,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 6</t>
+          <t xml:space="preserve">mda mpg ox</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">46.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7085,22 +7145,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-18</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.04.26</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7125,7 +7180,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-19</t>
         </is>
       </c>
     </row>
@@ -7142,22 +7197,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 6</t>
+          <t xml:space="preserve">u2os mpg ox</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">45.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7167,22 +7222,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-29</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.04.26</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7207,7 +7257,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-20</t>
         </is>
       </c>
     </row>
@@ -7224,32 +7274,42 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda mpg ox</t>
+          <t xml:space="preserve">hek mpg ox</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.05.26</t>
+          <t xml:space="preserve">17.02.26</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7279,7 +7339,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-21</t>
         </is>
       </c>
     </row>
@@ -7296,22 +7356,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 5</t>
+          <t xml:space="preserve">hek mpg ox</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7321,12 +7381,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-29</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.04.26</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -7336,7 +7396,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7361,7 +7421,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-22</t>
         </is>
       </c>
     </row>
@@ -7378,22 +7438,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 5</t>
+          <t xml:space="preserve">u2os mpg ox</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7401,24 +7461,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-17</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.05.26</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7443,7 +7498,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-23</t>
         </is>
       </c>
     </row>
@@ -7460,22 +7515,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 5</t>
+          <t xml:space="preserve">hek mpg ox</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7483,14 +7538,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-17</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.05.26</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7500,7 +7555,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7525,7 +7580,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-24</t>
         </is>
       </c>
     </row>
@@ -7542,22 +7597,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 5</t>
+          <t xml:space="preserve">mda mpg ox</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7565,24 +7620,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-17</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">01.05.26</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7607,7 +7657,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-25</t>
         </is>
       </c>
     </row>
@@ -7624,22 +7674,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">u2os mpg ox</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7649,12 +7699,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-15</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.05.26</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7684,7 +7734,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-26</t>
         </is>
       </c>
     </row>
@@ -7701,22 +7751,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">mda mpg ox</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7726,12 +7776,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-15</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.05.26</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7761,7 +7811,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-27</t>
         </is>
       </c>
     </row>
@@ -7778,22 +7828,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">u2os mpg ox</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7803,12 +7853,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-15</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.05.26</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7838,7 +7888,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-28</t>
         </is>
       </c>
     </row>
@@ -7855,22 +7905,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda mpg ox</t>
+          <t xml:space="preserve">u2os dox nek2</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.0</t>
+          <t xml:space="preserve">10.0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7880,12 +7930,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-04-27</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.05.26</t>
+          <t xml:space="preserve">27.04.26</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7915,7 +7965,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-29</t>
         </is>
       </c>
     </row>
@@ -7932,22 +7982,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda mpg ox</t>
+          <t xml:space="preserve">hek nek2 ox</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7955,14 +8005,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-26</t>
-        </is>
-      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.05.26</t>
+          <t xml:space="preserve">04.08.25</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7992,7 +8047,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-30</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8064,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8024,7 +8079,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">3.0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8032,14 +8087,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-25</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.05.26</t>
+          <t xml:space="preserve">01.08.25</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8074,7 +8129,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-31</t>
         </is>
       </c>
     </row>
@@ -8091,47 +8146,37 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">u2os nek2 ko b9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25</t>
+          <t xml:space="preserve">2025-01-23</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.05.26</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">23.01.25</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8156,7 +8201,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-32</t>
         </is>
       </c>
     </row>
@@ -8173,22 +8218,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 k37r</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8198,22 +8243,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25</t>
+          <t xml:space="preserve">2025-05-30</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.05.26</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">30.05.25</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8238,7 +8278,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-33</t>
         </is>
       </c>
     </row>
@@ -8255,22 +8295,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 ko b5</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">2.0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8280,22 +8320,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25</t>
+          <t xml:space="preserve">2025-01-22</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.05.26</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">22.01.25</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8320,7 +8355,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-34</t>
         </is>
       </c>
     </row>
@@ -8337,22 +8372,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 k37r</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">2.0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -8362,17 +8397,17 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25</t>
+          <t xml:space="preserve">2025-01-22</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.05.26</t>
+          <t xml:space="preserve">22.01.25</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8397,7 +8432,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-35</t>
         </is>
       </c>
     </row>
@@ -8414,22 +8449,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 k37r</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">16.0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8439,17 +8474,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25</t>
+          <t xml:space="preserve">2025-05-30</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.05.26</t>
+          <t xml:space="preserve">30.05.25</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8474,7 +8509,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-36</t>
         </is>
       </c>
     </row>
@@ -8491,22 +8526,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 ko b9</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">2.0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8516,17 +8551,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25</t>
+          <t xml:space="preserve">2025-01-22</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.05.26</t>
+          <t xml:space="preserve">22.01.25</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8551,7 +8586,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-37</t>
         </is>
       </c>
     </row>
@@ -8568,22 +8603,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda mpg ox</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.0</t>
+          <t xml:space="preserve">3.0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8591,14 +8626,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-26</t>
-        </is>
-      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.05.26</t>
+          <t xml:space="preserve">04.08.25</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8628,7 +8663,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-38</t>
         </is>
       </c>
     </row>
@@ -8645,22 +8680,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox mpg 3</t>
+          <t xml:space="preserve">hek nek2 ox</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">9.0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8668,14 +8703,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-29</t>
-        </is>
-      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
+          <t xml:space="preserve">01.08.25</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8705,7 +8745,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-39</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8762,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8737,7 +8777,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">3.0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8745,14 +8785,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-28</t>
-        </is>
-      </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.05.26</t>
+          <t xml:space="preserve">01.08.25</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -8787,7 +8827,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-40</t>
         </is>
       </c>
     </row>
@@ -8804,22 +8844,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 ox</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8829,17 +8869,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-28</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.05.26</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8869,7 +8904,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-41</t>
         </is>
       </c>
     </row>
@@ -8886,22 +8921,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 ox</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8911,17 +8946,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-28</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.05.26</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8951,7 +8981,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-42</t>
         </is>
       </c>
     </row>
@@ -8968,22 +8998,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 ox</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8993,12 +9023,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-28</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.05.26</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9028,7 +9058,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-43</t>
         </is>
       </c>
     </row>
@@ -9045,22 +9075,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 ox</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -9070,12 +9100,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-28</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.05.26</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9105,7 +9135,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-44</t>
         </is>
       </c>
     </row>
@@ -9122,22 +9152,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox</t>
+          <t xml:space="preserve">u2os nek2 ox</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -9147,12 +9177,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-28</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.05.26</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9182,7 +9212,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-45</t>
         </is>
       </c>
     </row>
@@ -9199,17 +9229,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox mpg 3</t>
+          <t xml:space="preserve">u2os nek2 ox</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -9224,12 +9254,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -9259,7 +9289,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-46</t>
         </is>
       </c>
     </row>
@@ -9276,17 +9306,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox mpg 3</t>
+          <t xml:space="preserve">u2os nek2 ox</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -9301,12 +9331,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -9336,7 +9366,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-47</t>
         </is>
       </c>
     </row>
@@ -9353,17 +9383,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox mpg 3</t>
+          <t xml:space="preserve">u2os nek2 ox</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -9378,12 +9408,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9413,7 +9443,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-48</t>
         </is>
       </c>
     </row>
@@ -9430,22 +9460,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox mpg 1</t>
+          <t xml:space="preserve">u2os dox nek2</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -9455,12 +9485,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9490,7 +9520,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-49</t>
         </is>
       </c>
     </row>
@@ -9507,17 +9537,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox mpg 1</t>
+          <t xml:space="preserve">u2os dox sh nek2</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9532,12 +9562,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9557,7 +9587,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -9567,7 +9597,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-50</t>
         </is>
       </c>
     </row>
@@ -9584,22 +9614,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox mpg 1</t>
+          <t xml:space="preserve">u2os dox nek2</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">8.0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9609,12 +9639,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29</t>
+          <t xml:space="preserve">2026-02-17</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
+          <t xml:space="preserve">17.02.26</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9644,7 +9674,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-51</t>
         </is>
       </c>
     </row>
@@ -9661,22 +9691,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox</t>
+          <t xml:space="preserve">u2os dox nek2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.0</t>
+          <t xml:space="preserve">10.0</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9686,17 +9716,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29</t>
+          <t xml:space="preserve">2026-04-27</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">27.04.26</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9726,7 +9751,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-52</t>
         </is>
       </c>
     </row>
@@ -9743,22 +9768,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox</t>
+          <t xml:space="preserve">mda nek2 ox</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9768,17 +9793,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29</t>
+          <t xml:space="preserve">2026-03-18</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">18.03.26</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9808,7 +9828,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-53</t>
         </is>
       </c>
     </row>
@@ -9825,22 +9845,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek apex1 ox</t>
+          <t xml:space="preserve">u2os nek2 ox</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.0</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9850,17 +9870,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-27</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.07.26</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9890,7 +9905,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-54</t>
         </is>
       </c>
     </row>
@@ -9907,22 +9922,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2 ox</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.0</t>
+          <t xml:space="preserve">11.0</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9932,17 +9947,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.05.26</t>
+          <t xml:space="preserve">13.03.26</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -9967,7 +9987,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-55</t>
         </is>
       </c>
     </row>
@@ -9984,22 +10004,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox</t>
+          <t xml:space="preserve">hek</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.0</t>
+          <t xml:space="preserve">11.0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -10009,12 +10029,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.05.26</t>
+          <t xml:space="preserve">13.03.26</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -10024,7 +10044,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10049,7 +10069,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-56</t>
         </is>
       </c>
     </row>
@@ -10066,37 +10086,32 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19.0</t>
+          <t xml:space="preserve">hek mtf1 ox</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-25</t>
+          <t xml:space="preserve">2025-07-22</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.06.26</t>
+          <t xml:space="preserve">22.07.25</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -10106,7 +10121,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10131,7 +10146,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-57</t>
         </is>
       </c>
     </row>
@@ -10148,22 +10163,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek apex1 ox</t>
+          <t xml:space="preserve">hek mtf1 ox 200</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.0</t>
+          <t xml:space="preserve">13.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -10173,12 +10188,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-15</t>
+          <t xml:space="preserve">2025-06-27</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.06.26</t>
+          <t xml:space="preserve">27.06.25</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -10213,7 +10228,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-58</t>
         </is>
       </c>
     </row>
@@ -10230,22 +10245,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek shgfp</t>
+          <t xml:space="preserve">hek mtf1 ox 50</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.0</t>
+          <t xml:space="preserve">17.0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -10255,12 +10270,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-15</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.06.26</t>
+          <t xml:space="preserve">19.05.25</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -10270,7 +10285,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10285,7 +10300,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -10295,7 +10310,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-59</t>
         </is>
       </c>
     </row>
@@ -10312,22 +10327,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda</t>
+          <t xml:space="preserve">hek mtf1 ox 100</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.0</t>
+          <t xml:space="preserve">17.0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -10337,17 +10352,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-25</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.06.26</t>
+          <t xml:space="preserve">19.05.25</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10372,7 +10392,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-60</t>
         </is>
       </c>
     </row>
@@ -10389,22 +10409,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox mpg</t>
+          <t xml:space="preserve">cal27 sh elk1 100</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">14.0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -10412,19 +10432,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-24</t>
-        </is>
-      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.07.26</t>
+          <t xml:space="preserve">10.09.25</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10439,7 +10459,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -10449,7 +10469,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-61</t>
         </is>
       </c>
     </row>
@@ -10466,22 +10486,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox mpg</t>
+          <t xml:space="preserve">cal27 sh elf1 100</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.0</t>
+          <t xml:space="preserve">20.0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -10489,19 +10509,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-24</t>
-        </is>
-      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.07.26</t>
+          <t xml:space="preserve">09.07.25</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10516,7 +10536,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -10526,7 +10546,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-62</t>
         </is>
       </c>
     </row>
@@ -10543,22 +10563,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda dox mpg</t>
+          <t xml:space="preserve">cal27 shgfp 100</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -10566,19 +10586,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-27</t>
-        </is>
-      </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.07.26</t>
+          <t xml:space="preserve">10.09.25</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10593,7 +10613,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -10603,7 +10623,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-63</t>
         </is>
       </c>
     </row>
@@ -10620,22 +10640,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek dox mpg</t>
+          <t xml:space="preserve">cal27 sh creb1 100</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10643,24 +10663,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-27</t>
-        </is>
-      </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.07.26</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">10.09.25</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10675,7 +10690,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -10685,7 +10700,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-64</t>
         </is>
       </c>
     </row>
@@ -10702,22 +10717,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda shgfp</t>
+          <t xml:space="preserve">cal27 sh klf4 100</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10725,14 +10740,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-27</t>
-        </is>
-      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.07.26</t>
+          <t xml:space="preserve">10.09.25</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10762,7 +10777,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-65</t>
         </is>
       </c>
     </row>
@@ -10779,22 +10794,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek shgfp</t>
+          <t xml:space="preserve">cal27 sh elf1 100</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10802,19 +10817,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-27</t>
-        </is>
-      </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.07.26</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">10.09.25</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10844,7 +10854,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-66</t>
         </is>
       </c>
     </row>
@@ -10861,22 +10871,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox sh nek2</t>
+          <t xml:space="preserve">hek mtf1 ox 200</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.0</t>
+          <t xml:space="preserve">19.0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10886,12 +10896,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-27</t>
+          <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.07.26</t>
+          <t xml:space="preserve">26.05.25</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10911,7 +10926,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -10921,7 +10936,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-67</t>
         </is>
       </c>
     </row>
@@ -10938,22 +10953,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2</t>
+          <t xml:space="preserve">cal27 sh klf4 200</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.0</t>
+          <t xml:space="preserve">20.0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10961,19 +10976,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-27</t>
-        </is>
-      </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.07.26</t>
+          <t xml:space="preserve">09.07.25</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -10988,7 +11003,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -10998,7 +11013,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-68</t>
         </is>
       </c>
     </row>
@@ -11015,22 +11030,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">cal27 sh elk1 100</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">20.0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11038,19 +11053,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-21</t>
-        </is>
-      </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">09.07.25</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -11070,7 +11080,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -11080,7 +11090,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-69</t>
         </is>
       </c>
     </row>
@@ -11097,22 +11107,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">cal27 sh creb1 100</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">20.0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -11120,19 +11130,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-21</t>
-        </is>
-      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">09.07.25</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -11152,7 +11157,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -11162,7 +11167,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-70</t>
         </is>
       </c>
     </row>
@@ -11179,22 +11184,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">cal27 shgfp 100</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.0</t>
+          <t xml:space="preserve">20.0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -11204,7 +11209,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">03.01.25</t>
+          <t xml:space="preserve">09.07.25</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -11212,11 +11217,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-71</t>
         </is>
       </c>
     </row>
@@ -11261,22 +11261,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 5</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">33.0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-11-21</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
+          <t xml:space="preserve">21.11.25</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-72</t>
         </is>
       </c>
     </row>
@@ -11343,22 +11343,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 8</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.0</t>
+          <t xml:space="preserve">43.0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-15</t>
+          <t xml:space="preserve">2024-11-21</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.05.25</t>
+          <t xml:space="preserve">21.11.24</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-73</t>
         </is>
       </c>
     </row>
@@ -11425,22 +11425,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek gnt</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.0</t>
+          <t xml:space="preserve">7.0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -11450,12 +11450,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-14</t>
+          <t xml:space="preserve">2025-04-18</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.02.25</t>
+          <t xml:space="preserve">18.04.25</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-74</t>
         </is>
       </c>
     </row>
@@ -11507,22 +11507,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 8 mtf1 ox</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">24.0</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -11530,14 +11530,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-21</t>
-        </is>
-      </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
+          <t xml:space="preserve">05.05.25</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-75</t>
         </is>
       </c>
     </row>
@@ -11589,22 +11589,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 8</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">55.0</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -11612,14 +11612,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-21</t>
-        </is>
-      </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
+          <t xml:space="preserve">06.01.25</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-76</t>
         </is>
       </c>
     </row>
@@ -11671,22 +11671,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 8</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.0</t>
+          <t xml:space="preserve">54.0</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">06.01.25</t>
+          <t xml:space="preserve">03.01.25</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-77</t>
         </is>
       </c>
     </row>
@@ -11753,22 +11753,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 6</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">43.0</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2024-11-21</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
+          <t xml:space="preserve">21.11.24</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-78</t>
         </is>
       </c>
     </row>
@@ -11835,22 +11835,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 8</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">48.0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11860,12 +11860,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-02-14</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
+          <t xml:space="preserve">14.02.25</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-79</t>
         </is>
       </c>
     </row>
@@ -11917,22 +11917,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 5</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">39.0</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11942,12 +11942,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-02-14</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
+          <t xml:space="preserve">14.02.25</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-80</t>
         </is>
       </c>
     </row>
@@ -11999,22 +11999,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 8</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">43.0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -12024,12 +12024,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2024-11-21</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
+          <t xml:space="preserve">21.11.24</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-81</t>
         </is>
       </c>
     </row>
@@ -12081,22 +12081,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek</t>
+          <t xml:space="preserve">hek ki 6</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.0</t>
+          <t xml:space="preserve">49.0</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2024-11-21</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.04.25</t>
+          <t xml:space="preserve">21.11.24</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-82</t>
         </is>
       </c>
     </row>
@@ -32769,17 +32769,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32797,10 +32797,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J14">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2</t>
+          <t xml:space="preserve">LiqNitro 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">LiqNitro 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32871,10 +32871,10 @@
         <v>81</v>
       </c>
       <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
         <v>81</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32908,10 +32908,10 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="J17">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32945,10 +32945,10 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="J18">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32547,17 +32547,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">LiqNitro 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -32631,7 +32631,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -32742,7 +32742,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32774,12 +32774,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32797,26 +32797,26 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32834,10 +32834,10 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J15">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32584,17 +32584,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">LiqNitro 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -32631,7 +32631,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -32742,7 +32742,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32811,12 +32811,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32834,26 +32834,26 @@
         <v>81</v>
       </c>
       <c r="I15">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32871,10 +32871,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J16">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -5746,12 +5746,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5828,12 +5828,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5905,12 +5905,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5982,12 +5982,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6059,12 +6059,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6141,12 +6141,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6223,12 +6223,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6305,12 +6305,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6387,12 +6387,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6469,12 +6469,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6551,12 +6551,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6633,12 +6633,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6710,12 +6710,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6792,12 +6792,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6874,12 +6874,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6951,12 +6951,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7033,12 +7033,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7110,12 +7110,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7187,12 +7187,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7264,12 +7264,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7346,12 +7346,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7428,12 +7428,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7505,12 +7505,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7587,12 +7587,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7664,12 +7664,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7741,12 +7741,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7818,12 +7818,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7895,12 +7895,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7972,12 +7972,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8054,12 +8054,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8136,12 +8136,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -8208,12 +8208,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8285,12 +8285,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8362,12 +8362,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8439,12 +8439,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8516,12 +8516,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8593,12 +8593,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -8670,12 +8670,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8752,12 +8752,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8834,12 +8834,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8911,12 +8911,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8988,12 +8988,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -9065,12 +9065,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9142,12 +9142,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9219,12 +9219,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9296,12 +9296,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -9373,12 +9373,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -9450,12 +9450,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9527,12 +9527,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9604,12 +9604,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9681,12 +9681,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -9758,12 +9758,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9835,12 +9835,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9912,12 +9912,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9994,12 +9994,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -10076,12 +10076,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -10153,12 +10153,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -10235,12 +10235,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -10317,12 +10317,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -10399,12 +10399,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10476,12 +10476,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10553,12 +10553,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10630,12 +10630,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10707,12 +10707,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10784,12 +10784,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10861,12 +10861,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -10943,12 +10943,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -11020,12 +11020,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -11097,12 +11097,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -11174,12 +11174,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -11251,12 +11251,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11333,12 +11333,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -11415,12 +11415,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -11497,12 +11497,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -11579,12 +11579,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -11661,12 +11661,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -11743,12 +11743,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11825,12 +11825,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11907,12 +11907,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11989,12 +11989,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -12071,12 +12071,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -32621,17 +32621,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -32649,10 +32649,10 @@
         <v>81</v>
       </c>
       <c r="I10">
+        <v>81</v>
+      </c>
+      <c r="J10">
         <v>0</v>
-      </c>
-      <c r="J10">
-        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -32742,7 +32742,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32848,12 +32848,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32871,26 +32871,26 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32908,10 +32908,10 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -12153,12 +12153,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -12230,12 +12230,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -12312,12 +12312,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -12394,12 +12394,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -12471,12 +12471,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -12548,12 +12548,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -12625,12 +12625,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -12702,12 +12702,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -12784,12 +12784,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -12866,12 +12866,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -12948,12 +12948,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -13025,12 +13025,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -13107,12 +13107,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -13189,12 +13189,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -13271,12 +13271,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -13353,12 +13353,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -13435,12 +13435,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -13517,12 +13517,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -13599,12 +13599,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -13681,12 +13681,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -13763,12 +13763,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -13845,12 +13845,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -13927,12 +13927,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -14009,12 +14009,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -32658,17 +32658,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -32686,10 +32686,10 @@
         <v>81</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J11">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -32742,7 +32742,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32885,12 +32885,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32908,26 +32908,26 @@
         <v>81</v>
       </c>
       <c r="I17">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32945,10 +32945,10 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="J18">
-        <v>57</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -201,7 +201,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -283,7 +283,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -365,7 +365,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -15610,7 +15610,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -16879,7 +16879,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -17161,7 +17161,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -18007,7 +18007,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -19323,7 +19323,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -19417,7 +19417,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -19511,7 +19511,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -19746,7 +19746,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -19840,7 +19840,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -20169,7 +20169,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -20357,7 +20357,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -20404,7 +20404,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -20639,7 +20639,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -21485,7 +21485,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -21579,7 +21579,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -21673,7 +21673,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -21861,7 +21861,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -21955,7 +21955,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -22237,7 +22237,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -22378,7 +22378,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -22425,7 +22425,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -22472,7 +22472,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -22566,7 +22566,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -23036,7 +23036,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -23177,7 +23177,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -23224,7 +23224,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -23365,7 +23365,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -23506,7 +23506,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -23647,7 +23647,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -23788,7 +23788,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -23835,7 +23835,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -23882,7 +23882,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -24023,7 +24023,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
@@ -24305,7 +24305,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
@@ -24493,7 +24493,7 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -24540,7 +24540,7 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
@@ -24681,7 +24681,7 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -24869,7 +24869,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -24916,7 +24916,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -25151,7 +25151,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -25245,7 +25245,7 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -25433,7 +25433,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -25480,7 +25480,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -25574,7 +25574,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -25621,7 +25621,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -25715,7 +25715,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -25762,7 +25762,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -25997,7 +25997,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -26091,7 +26091,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -26138,7 +26138,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -26185,7 +26185,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -26232,7 +26232,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -26279,7 +26279,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -26326,7 +26326,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -26373,7 +26373,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -26420,7 +26420,7 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -26514,7 +26514,7 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
@@ -26655,7 +26655,7 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
@@ -26702,7 +26702,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
@@ -26749,7 +26749,7 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
@@ -26796,7 +26796,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -26843,7 +26843,7 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -27125,7 +27125,7 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M454" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -27219,7 +27219,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -27360,7 +27360,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -27407,7 +27407,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -27501,7 +27501,7 @@
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M462" t="inlineStr">
@@ -27548,7 +27548,7 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M464" t="inlineStr">
@@ -27642,7 +27642,7 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -27736,7 +27736,7 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -27924,7 +27924,7 @@
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
@@ -27971,7 +27971,7 @@
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -28018,7 +28018,7 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -28206,7 +28206,7 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -28253,7 +28253,7 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
@@ -28300,7 +28300,7 @@
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -28347,7 +28347,7 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
@@ -28394,7 +28394,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
@@ -28441,7 +28441,7 @@
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M482" t="inlineStr">
@@ -28488,7 +28488,7 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
@@ -28535,7 +28535,7 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
@@ -28582,7 +28582,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M486" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
@@ -28723,7 +28723,7 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
@@ -28817,7 +28817,7 @@
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
@@ -28864,7 +28864,7 @@
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
@@ -28958,7 +28958,7 @@
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M493" t="inlineStr">
@@ -29005,7 +29005,7 @@
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
@@ -29099,7 +29099,7 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
@@ -29146,7 +29146,7 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M497" t="inlineStr">
@@ -29193,7 +29193,7 @@
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M498" t="inlineStr">
@@ -29240,7 +29240,7 @@
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
@@ -29287,7 +29287,7 @@
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M500" t="inlineStr">
@@ -29334,7 +29334,7 @@
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
@@ -29381,7 +29381,7 @@
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M502" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
@@ -29475,7 +29475,7 @@
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M504" t="inlineStr">
@@ -29522,7 +29522,7 @@
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M505" t="inlineStr">
@@ -29569,7 +29569,7 @@
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M506" t="inlineStr">
@@ -29616,7 +29616,7 @@
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -211,7 +211,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -293,7 +293,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -375,7 +375,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -17218,7 +17218,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -17453,7 +17453,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -17500,7 +17500,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -17547,7 +17547,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -17594,7 +17594,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -17829,7 +17829,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -18205,7 +18205,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -18581,7 +18581,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -19145,7 +19145,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -19333,7 +19333,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -19521,7 +19521,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -19662,7 +19662,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -20320,7 +20320,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -20414,7 +20414,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -20555,7 +20555,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
@@ -20696,7 +20696,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
@@ -20743,7 +20743,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -20790,7 +20790,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -20837,7 +20837,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -20884,7 +20884,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
@@ -20978,7 +20978,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -21025,7 +21025,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -21119,7 +21119,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
@@ -21307,7 +21307,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
@@ -21401,7 +21401,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -21542,7 +21542,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
@@ -22012,7 +22012,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
@@ -22059,7 +22059,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -22247,7 +22247,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -22529,7 +22529,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
@@ -22811,7 +22811,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
@@ -22858,7 +22858,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O365" t="inlineStr">
@@ -22999,7 +22999,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -23281,7 +23281,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -23328,7 +23328,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
@@ -23375,7 +23375,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -23422,7 +23422,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -23610,7 +23610,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O388" t="inlineStr">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
@@ -24127,7 +24127,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O394" t="inlineStr">
@@ -24362,7 +24362,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O395" t="inlineStr">
@@ -24409,7 +24409,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O396" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O398" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O399" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O400" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O401" t="inlineStr">
@@ -24691,7 +24691,7 @@
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O402" t="inlineStr">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O403" t="inlineStr">
@@ -24785,7 +24785,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O404" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -24973,7 +24973,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
@@ -25020,7 +25020,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
@@ -25067,7 +25067,7 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O410" t="inlineStr">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O411" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -25255,7 +25255,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O414" t="inlineStr">
@@ -25302,7 +25302,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -25349,7 +25349,7 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O416" t="inlineStr">
@@ -25396,7 +25396,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O418" t="inlineStr">
@@ -25490,7 +25490,7 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O419" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O420" t="inlineStr">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O421" t="inlineStr">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O422" t="inlineStr">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O423" t="inlineStr">
@@ -25725,7 +25725,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O424" t="inlineStr">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O425" t="inlineStr">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
@@ -25866,7 +25866,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
@@ -26007,7 +26007,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O431" t="inlineStr">
@@ -26101,7 +26101,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O434" t="inlineStr">
@@ -26242,7 +26242,7 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O435" t="inlineStr">
@@ -26289,7 +26289,7 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O436" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
@@ -26383,7 +26383,7 @@
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O438" t="inlineStr">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
@@ -26524,7 +26524,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O441" t="inlineStr">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O442" t="inlineStr">
@@ -26618,7 +26618,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O443" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O444" t="inlineStr">
@@ -26712,7 +26712,7 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
@@ -26759,7 +26759,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -26806,7 +26806,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O447" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O449" t="inlineStr">
@@ -26947,7 +26947,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O450" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O451" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O452" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
@@ -27135,7 +27135,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O454" t="inlineStr">
@@ -27182,7 +27182,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O455" t="inlineStr">
@@ -27229,7 +27229,7 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O456" t="inlineStr">
@@ -27276,7 +27276,7 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O457" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O458" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O459" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O460" t="inlineStr">
@@ -27464,7 +27464,7 @@
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O461" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O462" t="inlineStr">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -27605,7 +27605,7 @@
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O464" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O466" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O467" t="inlineStr">
@@ -27793,7 +27793,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O468" t="inlineStr">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O469" t="inlineStr">
@@ -27887,7 +27887,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
@@ -27934,7 +27934,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
@@ -28075,7 +28075,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
@@ -28122,7 +28122,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
@@ -28169,7 +28169,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
@@ -28216,7 +28216,7 @@
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O477" t="inlineStr">
@@ -28263,7 +28263,7 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
@@ -28310,7 +28310,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
@@ -28357,7 +28357,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
@@ -28404,7 +28404,7 @@
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O481" t="inlineStr">
@@ -28451,7 +28451,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O482" t="inlineStr">
@@ -28498,7 +28498,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -28545,7 +28545,7 @@
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O484" t="inlineStr">
@@ -28592,7 +28592,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O485" t="inlineStr">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
@@ -28686,7 +28686,7 @@
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O487" t="inlineStr">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
@@ -28780,7 +28780,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
@@ -28827,7 +28827,7 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O490" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O491" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O493" t="inlineStr">
@@ -29015,7 +29015,7 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O494" t="inlineStr">
@@ -29062,7 +29062,7 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O495" t="inlineStr">
@@ -29109,7 +29109,7 @@
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O496" t="inlineStr">
@@ -29156,7 +29156,7 @@
       </c>
       <c r="N497" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O497" t="inlineStr">
@@ -29203,7 +29203,7 @@
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O498" t="inlineStr">
@@ -29250,7 +29250,7 @@
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O499" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O500" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O501" t="inlineStr">
@@ -29391,7 +29391,7 @@
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O502" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="N503" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O503" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O504" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O505" t="inlineStr">
@@ -29579,7 +29579,7 @@
       </c>
       <c r="N506" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O506" t="inlineStr">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No CASPEX</t>
         </is>
       </c>
       <c r="O507" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -216,7 +216,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -298,7 +298,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -380,7 +380,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -14309,7 +14309,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -14779,7 +14779,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
@@ -15625,7 +15625,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -15719,7 +15719,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -16283,7 +16283,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -16941,7 +16941,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
@@ -17364,7 +17364,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -17693,7 +17693,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -17834,7 +17834,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -18022,7 +18022,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -18069,7 +18069,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -18445,7 +18445,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -19009,7 +19009,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -19056,7 +19056,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -19385,7 +19385,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -19479,7 +19479,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -19573,7 +19573,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -19620,7 +19620,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -19667,7 +19667,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -19761,7 +19761,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -20278,7 +20278,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -20607,7 +20607,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -20701,7 +20701,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -20795,7 +20795,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -21265,7 +21265,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -21688,7 +21688,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -21782,7 +21782,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -21829,7 +21829,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -21923,7 +21923,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -22158,7 +22158,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -22393,7 +22393,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -22675,7 +22675,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -22769,7 +22769,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -22816,7 +22816,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -22863,7 +22863,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -23098,7 +23098,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -23145,7 +23145,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
@@ -23239,7 +23239,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
@@ -23333,7 +23333,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
@@ -23380,7 +23380,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
@@ -23427,7 +23427,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R375" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R376" t="inlineStr">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
@@ -23568,7 +23568,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R378" t="inlineStr">
@@ -23615,7 +23615,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R379" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R380" t="inlineStr">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R381" t="inlineStr">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R382" t="inlineStr">
@@ -23803,7 +23803,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R383" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R384" t="inlineStr">
@@ -23897,7 +23897,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R385" t="inlineStr">
@@ -23944,7 +23944,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R386" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R387" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R388" t="inlineStr">
@@ -24085,7 +24085,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R389" t="inlineStr">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R390" t="inlineStr">
@@ -24179,7 +24179,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R391" t="inlineStr">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R392" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R393" t="inlineStr">
@@ -24320,7 +24320,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R394" t="inlineStr">
@@ -24367,7 +24367,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R395" t="inlineStr">
@@ -24414,7 +24414,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R396" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R397" t="inlineStr">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R398" t="inlineStr">
@@ -24555,7 +24555,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R399" t="inlineStr">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R400" t="inlineStr">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R401" t="inlineStr">
@@ -24696,7 +24696,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R402" t="inlineStr">
@@ -24743,7 +24743,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R403" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R404" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R405" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R406" t="inlineStr">
@@ -24931,7 +24931,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R407" t="inlineStr">
@@ -24978,7 +24978,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R408" t="inlineStr">
@@ -25025,7 +25025,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R409" t="inlineStr">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R410" t="inlineStr">
@@ -25119,7 +25119,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R411" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R412" t="inlineStr">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R413" t="inlineStr">
@@ -25260,7 +25260,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R414" t="inlineStr">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R415" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R416" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R417" t="inlineStr">
@@ -25448,7 +25448,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R418" t="inlineStr">
@@ -25495,7 +25495,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R419" t="inlineStr">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R420" t="inlineStr">
@@ -25589,7 +25589,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R421" t="inlineStr">
@@ -25636,7 +25636,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R422" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R423" t="inlineStr">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R424" t="inlineStr">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R425" t="inlineStr">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R426" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R427" t="inlineStr">
@@ -25918,7 +25918,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R428" t="inlineStr">
@@ -25965,7 +25965,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R429" t="inlineStr">
@@ -26012,7 +26012,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R430" t="inlineStr">
@@ -26059,7 +26059,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R431" t="inlineStr">
@@ -26106,7 +26106,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R432" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R433" t="inlineStr">
@@ -26200,7 +26200,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -26247,7 +26247,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R435" t="inlineStr">
@@ -26294,7 +26294,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R436" t="inlineStr">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R437" t="inlineStr">
@@ -26388,7 +26388,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R438" t="inlineStr">
@@ -26435,7 +26435,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R439" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R440" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R441" t="inlineStr">
@@ -26576,7 +26576,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R442" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R443" t="inlineStr">
@@ -26670,7 +26670,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R444" t="inlineStr">
@@ -26717,7 +26717,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R445" t="inlineStr">
@@ -26764,7 +26764,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R446" t="inlineStr">
@@ -26811,7 +26811,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R447" t="inlineStr">
@@ -26858,7 +26858,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R448" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R449" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R450" t="inlineStr">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R451" t="inlineStr">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R452" t="inlineStr">
@@ -27093,7 +27093,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R453" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R454" t="inlineStr">
@@ -27187,7 +27187,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R455" t="inlineStr">
@@ -27234,7 +27234,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R456" t="inlineStr">
@@ -27281,7 +27281,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R457" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R458" t="inlineStr">
@@ -27375,7 +27375,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R459" t="inlineStr">
@@ -27422,7 +27422,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R460" t="inlineStr">
@@ -27469,7 +27469,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R461" t="inlineStr">
@@ -27516,7 +27516,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R462" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R463" t="inlineStr">
@@ -27610,7 +27610,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R464" t="inlineStr">
@@ -27657,7 +27657,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R465" t="inlineStr">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R466" t="inlineStr">
@@ -27751,7 +27751,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R467" t="inlineStr">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R468" t="inlineStr">
@@ -27845,7 +27845,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R469" t="inlineStr">
@@ -27892,7 +27892,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R470" t="inlineStr">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R471" t="inlineStr">
@@ -27986,7 +27986,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R472" t="inlineStr">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R473" t="inlineStr">
@@ -28080,7 +28080,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R474" t="inlineStr">
@@ -28127,7 +28127,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R475" t="inlineStr">
@@ -28174,7 +28174,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R476" t="inlineStr">
@@ -28221,7 +28221,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R477" t="inlineStr">
@@ -28268,7 +28268,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R478" t="inlineStr">
@@ -28315,7 +28315,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R479" t="inlineStr">
@@ -28362,7 +28362,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R480" t="inlineStr">
@@ -28409,7 +28409,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R481" t="inlineStr">
@@ -28456,7 +28456,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R482" t="inlineStr">
@@ -28503,7 +28503,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R483" t="inlineStr">
@@ -28550,7 +28550,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R484" t="inlineStr">
@@ -28597,7 +28597,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R485" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R486" t="inlineStr">
@@ -28691,7 +28691,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R487" t="inlineStr">
@@ -28738,7 +28738,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R488" t="inlineStr">
@@ -28785,7 +28785,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R489" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R490" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R491" t="inlineStr">
@@ -28926,7 +28926,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R492" t="inlineStr">
@@ -28973,7 +28973,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R493" t="inlineStr">
@@ -29020,7 +29020,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R494" t="inlineStr">
@@ -29067,7 +29067,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R495" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R496" t="inlineStr">
@@ -29161,7 +29161,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R497" t="inlineStr">
@@ -29208,7 +29208,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R498" t="inlineStr">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R499" t="inlineStr">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R500" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R501" t="inlineStr">
@@ -29396,7 +29396,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R502" t="inlineStr">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R503" t="inlineStr">
@@ -29490,7 +29490,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R504" t="inlineStr">
@@ -29537,7 +29537,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R505" t="inlineStr">
@@ -29584,7 +29584,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R506" t="inlineStr">
@@ -29631,7 +29631,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No guide/sh</t>
         </is>
       </c>
       <c r="R507" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32951,6 +32951,228 @@
         <v>11</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChIP Box</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>9</v>
+      </c>
+      <c r="G19">
+        <v>9</v>
+      </c>
+      <c r="H19">
+        <v>81</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChIP Box -2-</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>9</v>
+      </c>
+      <c r="H20">
+        <v>81</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut -20 -2-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>9</v>
+      </c>
+      <c r="G21">
+        <v>9</v>
+      </c>
+      <c r="H21">
+        <v>81</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <v>9</v>
+      </c>
+      <c r="H22">
+        <v>81</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unkown FOR NOW</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>9</v>
+      </c>
+      <c r="G23">
+        <v>9</v>
+      </c>
+      <c r="H23">
+        <v>81</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No use</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>9</v>
+      </c>
+      <c r="H24">
+        <v>81</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32695,17 +32695,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -32742,7 +32742,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32945,26 +32945,26 @@
         <v>81</v>
       </c>
       <c r="I18">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -32982,10 +32982,10 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J19">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32732,17 +32732,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32959,12 +32959,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -32982,26 +32982,26 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33019,10 +33019,10 @@
         <v>81</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J20">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32769,17 +32769,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -32996,12 +32996,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33019,26 +33019,26 @@
         <v>81</v>
       </c>
       <c r="I20">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -33056,10 +33056,10 @@
         <v>81</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J21">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32806,17 +32806,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33033,12 +33033,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -33056,26 +33056,26 @@
         <v>81</v>
       </c>
       <c r="I21">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -33093,10 +33093,10 @@
         <v>81</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J22">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32732,17 +32732,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32769,17 +32769,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32806,17 +32806,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32959,12 +32959,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -32982,26 +32982,26 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J19">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33028,17 +33028,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -33065,17 +33065,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -33093,10 +33093,10 @@
         <v>81</v>
       </c>
       <c r="I22">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32705,7 +32705,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32705,7 +32705,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -32732,17 +32732,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32959,12 +32959,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -32982,26 +32982,26 @@
         <v>81</v>
       </c>
       <c r="I19">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33019,10 +33019,10 @@
         <v>81</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J20">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32325,7 +32325,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -32335,7 +32335,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CAA CELLS</t>
+          <t xml:space="preserve">LiqNitro 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -32362,7 +32362,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -32372,7 +32372,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">LiqNitro 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -32399,17 +32399,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -32427,26 +32427,26 @@
         <v>81</v>
       </c>
       <c r="I4">
+        <v>81</v>
+      </c>
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="J4">
-        <v>81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONGOING</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -32464,16 +32464,16 @@
         <v>81</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J5">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -32483,7 +32483,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -32510,17 +32510,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -32547,7 +32547,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquid Nitrogen</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -32557,7 +32557,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32584,7 +32584,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquid Nitrogen</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -32621,17 +32621,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquid Nitrogen</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -32649,26 +32649,26 @@
         <v>81</v>
       </c>
       <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <v>81</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquid Nitrogen</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -32686,26 +32686,26 @@
         <v>81</v>
       </c>
       <c r="I11">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -32732,17 +32732,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32769,17 +32769,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32806,17 +32806,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32848,12 +32848,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32871,26 +32871,26 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J16">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">UMUT CAA CELLS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32917,17 +32917,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32954,17 +32954,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">DUZENLE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -32991,17 +32991,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">ONGOING</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33028,17 +33028,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -33065,17 +33065,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -33093,10 +33093,10 @@
         <v>81</v>
       </c>
       <c r="I22">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32473,17 +32473,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -32510,17 +32510,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -32547,17 +32547,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32584,17 +32584,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -32631,7 +32631,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -32700,12 +32700,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -32723,26 +32723,26 @@
         <v>81</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J12">
-        <v>81</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">UMUT CAA CELLS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -32769,17 +32769,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -32806,17 +32806,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">DUZENLE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -32843,17 +32843,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">ONGOING</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -32871,10 +32871,10 @@
         <v>81</v>
       </c>
       <c r="I16">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CAA CELLS</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32954,7 +32954,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -32991,7 +32991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONGOING</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -33038,7 +33038,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -33065,17 +33065,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -211,7 +211,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -293,7 +293,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -375,7 +375,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -17218,7 +17218,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -17453,7 +17453,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -17500,7 +17500,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -17547,7 +17547,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -17594,7 +17594,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -17829,7 +17829,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -18205,7 +18205,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -18581,7 +18581,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -19145,7 +19145,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -19333,7 +19333,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -19521,7 +19521,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -19662,7 +19662,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -20320,7 +20320,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -20414,7 +20414,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -20555,7 +20555,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
@@ -20696,7 +20696,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
@@ -20743,7 +20743,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -20790,7 +20790,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -20837,7 +20837,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -20884,7 +20884,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
@@ -20978,7 +20978,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -21025,7 +21025,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -21119,7 +21119,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
@@ -21307,7 +21307,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
@@ -21401,7 +21401,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -21542,7 +21542,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
@@ -22012,7 +22012,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
@@ -22059,7 +22059,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -22247,7 +22247,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -22529,7 +22529,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
@@ -22811,7 +22811,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
@@ -22858,7 +22858,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O365" t="inlineStr">
@@ -22999,7 +22999,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -23281,7 +23281,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -23328,7 +23328,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
@@ -23375,7 +23375,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -23422,7 +23422,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -23610,7 +23610,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O388" t="inlineStr">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
@@ -24127,7 +24127,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O394" t="inlineStr">
@@ -24362,7 +24362,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O395" t="inlineStr">
@@ -24409,7 +24409,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O396" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O398" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O399" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O400" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O401" t="inlineStr">
@@ -24691,7 +24691,7 @@
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O402" t="inlineStr">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O403" t="inlineStr">
@@ -24785,7 +24785,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O404" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -24973,7 +24973,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
@@ -25020,7 +25020,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
@@ -25067,7 +25067,7 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O410" t="inlineStr">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O411" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -25255,7 +25255,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O414" t="inlineStr">
@@ -25302,7 +25302,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -25349,7 +25349,7 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O416" t="inlineStr">
@@ -25396,7 +25396,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O418" t="inlineStr">
@@ -25490,7 +25490,7 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O419" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O420" t="inlineStr">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O421" t="inlineStr">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O422" t="inlineStr">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O423" t="inlineStr">
@@ -25725,7 +25725,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O424" t="inlineStr">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O425" t="inlineStr">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
@@ -25866,7 +25866,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
@@ -26007,7 +26007,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O431" t="inlineStr">
@@ -26101,7 +26101,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O434" t="inlineStr">
@@ -26242,7 +26242,7 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O435" t="inlineStr">
@@ -26289,7 +26289,7 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O436" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
@@ -26383,7 +26383,7 @@
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O438" t="inlineStr">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
@@ -26524,7 +26524,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O441" t="inlineStr">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O442" t="inlineStr">
@@ -26618,7 +26618,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O443" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O444" t="inlineStr">
@@ -26712,7 +26712,7 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
@@ -26759,7 +26759,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -26806,7 +26806,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O447" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O449" t="inlineStr">
@@ -26947,7 +26947,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O450" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O451" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O452" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
@@ -27135,7 +27135,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O454" t="inlineStr">
@@ -27182,7 +27182,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O455" t="inlineStr">
@@ -27229,7 +27229,7 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O456" t="inlineStr">
@@ -27276,7 +27276,7 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O457" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O458" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O459" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O460" t="inlineStr">
@@ -27464,7 +27464,7 @@
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O461" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O462" t="inlineStr">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -27605,7 +27605,7 @@
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O464" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O466" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O467" t="inlineStr">
@@ -27793,7 +27793,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O468" t="inlineStr">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O469" t="inlineStr">
@@ -27887,7 +27887,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
@@ -27934,7 +27934,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
@@ -28075,7 +28075,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
@@ -28122,7 +28122,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
@@ -28169,7 +28169,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
@@ -28216,7 +28216,7 @@
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O477" t="inlineStr">
@@ -28263,7 +28263,7 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
@@ -28310,7 +28310,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
@@ -28357,7 +28357,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
@@ -28404,7 +28404,7 @@
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O481" t="inlineStr">
@@ -28451,7 +28451,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O482" t="inlineStr">
@@ -28498,7 +28498,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -28545,7 +28545,7 @@
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O484" t="inlineStr">
@@ -28592,7 +28592,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O485" t="inlineStr">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
@@ -28686,7 +28686,7 @@
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O487" t="inlineStr">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
@@ -28780,7 +28780,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
@@ -28827,7 +28827,7 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O490" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O491" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O493" t="inlineStr">
@@ -29015,7 +29015,7 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O494" t="inlineStr">
@@ -29062,7 +29062,7 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O495" t="inlineStr">
@@ -29109,7 +29109,7 @@
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O496" t="inlineStr">
@@ -29156,7 +29156,7 @@
       </c>
       <c r="N497" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O497" t="inlineStr">
@@ -29203,7 +29203,7 @@
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O498" t="inlineStr">
@@ -29250,7 +29250,7 @@
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O499" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O500" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O501" t="inlineStr">
@@ -29391,7 +29391,7 @@
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O502" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="N503" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O503" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O504" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O505" t="inlineStr">
@@ -29579,7 +29579,7 @@
       </c>
       <c r="N506" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O506" t="inlineStr">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t xml:space="preserve">No CASPEX</t>
+          <t xml:space="preserve">No Casp</t>
         </is>
       </c>
       <c r="O507" t="inlineStr">

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32922,12 +32922,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">Umut Cell Box -5-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -32954,17 +32954,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33038,7 +33038,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -33075,7 +33075,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -33102,17 +33102,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unkown FOR NOW</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -33149,7 +33149,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">No use</t>
+          <t xml:space="preserve">Unkown FOR NOW</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -33170,6 +33170,43 @@
         <v>0</v>
       </c>
       <c r="J24">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No use</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>9</v>
+      </c>
+      <c r="G25">
+        <v>9</v>
+      </c>
+      <c r="H25">
+        <v>81</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>81</v>
       </c>
     </row>

--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -33210,6 +33210,43 @@
         <v>81</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Big Plasmid Box</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>9</v>
+      </c>
+      <c r="H26">
+        <v>81</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/beyzat.xlsx
+++ b/cellstocks/data/beyzat.xlsx
@@ -32959,12 +32959,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 2</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">Big Plasmid Box</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -32991,17 +32991,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33038,7 +33038,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -33075,7 +33075,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -33112,7 +33112,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -33139,17 +33139,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unkown FOR NOW</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -33186,7 +33186,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">No use</t>
+          <t xml:space="preserve">Unkown FOR NOW</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -33223,7 +33223,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Plasmid Box</t>
+          <t xml:space="preserve">No use</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
